--- a/data/Verzasca/cost/total_demand.xlsx
+++ b/data/Verzasca/cost/total_demand.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>98736.72893790888</v>
+        <v>4114.03037241287</v>
       </c>
     </row>
     <row r="3">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>47955.66626676168</v>
+        <v>1998.15276111507</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>488173.9723980546</v>
+        <v>20340.58218325227</v>
       </c>
     </row>
   </sheetData>
